--- a/public/Human-Friendly Excel Structure - ex.xlsx
+++ b/public/Human-Friendly Excel Structure - ex.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rushi\internship manual\project\next_adwait_tour\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0095286A-DC75-43AD-B588-84D2690C336F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18039F23-D02E-4CF2-BF81-3E8B2FD307B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Human-Friendly Excel Structure" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>Hotel Name</t>
   </si>
@@ -76,12 +87,6 @@
     <t>Extra Bed (A)</t>
   </si>
   <si>
-    <t>OCP</t>
-  </si>
-  <si>
-    <t>---</t>
-  </si>
-  <si>
     <t>Fariyas Resort</t>
   </si>
   <si>
@@ -112,7 +117,13 @@
     <t>off season</t>
   </si>
   <si>
-    <t>off seasons</t>
+    <t>season 1</t>
+  </si>
+  <si>
+    <t>season 2</t>
+  </si>
+  <si>
+    <t>season 3</t>
   </si>
 </sst>
 </file>
@@ -383,9 +394,9 @@
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -418,12 +429,12 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -432,7 +443,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2">
         <v>46023</v>
@@ -459,7 +470,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
@@ -479,7 +490,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="G4" s="1" t="s">
         <v>16</v>
       </c>
@@ -499,9 +510,9 @@
         <v>5700</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2">
         <v>46211</v>
@@ -528,7 +539,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
@@ -548,7 +559,7 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
@@ -577,7 +588,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
@@ -597,50 +608,28 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>19</v>
-      </c>
+    <row r="9" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>12</v>
@@ -655,7 +644,7 @@
         <v>13</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I10" s="1">
         <v>8500</v>
@@ -665,6 +654,9 @@
       </c>
       <c r="K10" s="1">
         <v>12000</v>
+      </c>
+      <c r="L10" s="1">
+        <v>15220</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -683,19 +675,22 @@
       <c r="K11" s="1">
         <v>4500</v>
       </c>
+      <c r="L11" s="1">
+        <v>5000</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E13" s="2">
         <v>46054</v>
@@ -707,7 +702,7 @@
         <v>13</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I13" s="1">
         <v>8500</v>
